--- a/Result/profitability/6578.xlsx
+++ b/Result/profitability/6578.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM42"/>
+  <dimension ref="A1:AM43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5764,6 +5764,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>107</v>
+      </c>
+      <c r="D43" t="n">
+        <v>79</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28</v>
+      </c>
+      <c r="F43" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>9.36%</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>12</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="N43" t="n">
+        <v>22.1475</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0.1898676403468735</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>-1.619047619047619</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>4.940000000000001</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.2337908187411264</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK43" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
